--- a/naver-place-crawler/results_hair/동래구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/동래구_미용실.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V433"/>
+  <dimension ref="A1:V434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -37627,40 +37627,44 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>머리염색</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>구피샵 부산사직점</t>
+          <t>모완10헤어 동래롯데점</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>euneun0616@naver.com</t>
+          <t>toy79s@naver.com</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
-      <c r="E398" t="inlineStr"/>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>0507-1307-0556</t>
+        </is>
+      </c>
       <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 사직북로 51 1층</t>
+          <t>부산광역시 동래구 동래로19번길 2 2층</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@toy1113s</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -37685,13 +37689,13 @@
         </is>
       </c>
       <c r="P398" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="Q398" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R398" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="S398" t="inlineStr">
         <is>
@@ -37700,12 +37704,12 @@
       </c>
       <c r="T398" t="inlineStr">
         <is>
-          <t>2017805632</t>
+          <t>34377827</t>
         </is>
       </c>
       <c r="U398" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2017805632</t>
+          <t>https://m.place.naver.com/place/34377827</t>
         </is>
       </c>
       <c r="V398" t="inlineStr">
@@ -37722,29 +37726,25 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>큐사랑 사직점</t>
+          <t>구피샵 부산사직점</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>young627072@naver.com</t>
+          <t>euneun0616@naver.com</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>0507-1425-4622</t>
-        </is>
-      </c>
+      <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
       <c r="G399" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 아시아드대로 147 2층</t>
+          <t>부산광역시 동래구 사직북로 51 1층</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/young627072</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -37754,12 +37754,12 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
@@ -37779,13 +37779,13 @@
         </is>
       </c>
       <c r="P399" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="Q399" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="R399" t="n">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="S399" t="inlineStr">
         <is>
@@ -37794,12 +37794,12 @@
       </c>
       <c r="T399" t="inlineStr">
         <is>
-          <t>1652647280</t>
+          <t>2017805632</t>
         </is>
       </c>
       <c r="U399" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1652647280</t>
+          <t>https://m.place.naver.com/place/2017805632</t>
         </is>
       </c>
       <c r="V399" t="inlineStr">
@@ -37811,34 +37811,34 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>미용</t>
+          <t>머리염색</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>미장원 태이</t>
+          <t>큐사랑 사직점</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>skydome11@naver.com</t>
+          <t>young627072@naver.com</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr">
         <is>
-          <t>0507-1382-6999</t>
+          <t>0507-1425-4622</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 아시아드대로161번길 28</t>
+          <t>부산광역시 동래구 아시아드대로 147 2층</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/young627072</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -37848,12 +37848,12 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
@@ -37873,13 +37873,13 @@
         </is>
       </c>
       <c r="P400" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="Q400" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="R400" t="n">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
@@ -37888,12 +37888,12 @@
       </c>
       <c r="T400" t="inlineStr">
         <is>
-          <t>1330890358</t>
+          <t>1652647280</t>
         </is>
       </c>
       <c r="U400" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330890358</t>
+          <t>https://m.place.naver.com/place/1652647280</t>
         </is>
       </c>
       <c r="V400" t="inlineStr">
@@ -37905,25 +37905,29 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>민영주차장</t>
+          <t>미용</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>제일 주차장</t>
+          <t>미장원 태이</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>se05211@naver.com</t>
+          <t>skydome11@naver.com</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
-      <c r="E401" t="inlineStr"/>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>0507-1382-6999</t>
+        </is>
+      </c>
       <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 칠산동 276-1 209-1, 209-3</t>
+          <t>부산광역시 동래구 아시아드대로161번길 28</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -37963,10 +37967,10 @@
         </is>
       </c>
       <c r="P401" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q401" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R401" t="n">
         <v>11</v>
@@ -37978,12 +37982,12 @@
       </c>
       <c r="T401" t="inlineStr">
         <is>
-          <t>1616043190</t>
+          <t>1330890358</t>
         </is>
       </c>
       <c r="U401" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616043190</t>
+          <t>https://m.place.naver.com/place/1330890358</t>
         </is>
       </c>
       <c r="V401" t="inlineStr">
@@ -37995,34 +37999,30 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>민영주차장</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>로운이네살롱</t>
+          <t>제일 주차장</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>sbsmile12@naver.com</t>
+          <t>se05211@naver.com</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>0507-1418-8079</t>
-        </is>
-      </c>
+      <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr"/>
       <c r="G402" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 사직로 70 1층 로운이네살롱</t>
+          <t>부산광역시 동래구 칠산동 276-1 209-1, 209-3</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/Rowoon_owner</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -38032,7 +38032,7 @@
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
@@ -38053,17 +38053,17 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P402" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="Q402" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="R402" t="n">
-        <v>136</v>
+        <v>11</v>
       </c>
       <c r="S402" t="inlineStr">
         <is>
@@ -38072,12 +38072,12 @@
       </c>
       <c r="T402" t="inlineStr">
         <is>
-          <t>1479182514</t>
+          <t>1616043190</t>
         </is>
       </c>
       <c r="U402" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1479182514</t>
+          <t>https://m.place.naver.com/place/1616043190</t>
         </is>
       </c>
       <c r="V402" t="inlineStr">
@@ -38094,25 +38094,29 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>따따시몽</t>
+          <t>로운이네살롱</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>dds_mong@naver.com</t>
+          <t>sbsmile12@naver.com</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
-      <c r="E403" t="inlineStr"/>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>0507-1418-8079</t>
+        </is>
+      </c>
       <c r="F403" t="inlineStr"/>
       <c r="G403" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 연안로59번길 11-2 1층</t>
+          <t>부산광역시 동래구 사직로 70 1층 로운이네살롱</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dds_mong</t>
+          <t>https://www.instagram.com/Rowoon_owner</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -38127,7 +38131,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -38147,13 +38151,13 @@
         </is>
       </c>
       <c r="P403" t="n">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="Q403" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="R403" t="n">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="S403" t="inlineStr">
         <is>
@@ -38162,12 +38166,12 @@
       </c>
       <c r="T403" t="inlineStr">
         <is>
-          <t>1769406601</t>
+          <t>1479182514</t>
         </is>
       </c>
       <c r="U403" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1769406601</t>
+          <t>https://m.place.naver.com/place/1479182514</t>
         </is>
       </c>
       <c r="V403" t="inlineStr">
@@ -38184,25 +38188,25 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>로제드퍼피</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr"/>
+          <t>따따시몽</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>dds_mong@naver.com</t>
+        </is>
+      </c>
       <c r="D404" t="inlineStr"/>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>0507-1462-0662</t>
-        </is>
-      </c>
+      <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 석사북로 61-1 1층 로제 드 퍼피 펫살롱</t>
+          <t>부산광역시 동래구 연안로59번길 11-2 1층</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/roses_de_puppy?igsh=MW1panAxaXphOXMxMQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/dds_mong</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -38217,7 +38221,7 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
@@ -38237,13 +38241,13 @@
         </is>
       </c>
       <c r="P404" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Q404" t="n">
         <v>0</v>
       </c>
       <c r="R404" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S404" t="inlineStr">
         <is>
@@ -38252,12 +38256,12 @@
       </c>
       <c r="T404" t="inlineStr">
         <is>
-          <t>2008641686</t>
+          <t>1769406601</t>
         </is>
       </c>
       <c r="U404" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2008641686</t>
+          <t>https://m.place.naver.com/place/1769406601</t>
         </is>
       </c>
       <c r="V404" t="inlineStr">
@@ -38274,29 +38278,25 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>깨독</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>koreai815@naver.com</t>
-        </is>
-      </c>
+          <t>로제드퍼피</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr">
         <is>
-          <t>0507-1361-2731</t>
+          <t>0507-1462-0662</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
       <c r="G405" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 사직로 80 222동 B206호</t>
+          <t>부산광역시 동래구 석사북로 61-1 1층 로제 드 퍼피 펫살롱</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/roses_de_puppy?igsh=MW1panAxaXphOXMxMQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -38306,7 +38306,7 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -38327,17 +38327,17 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q405" t="n">
         <v>0</v>
       </c>
       <c r="R405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S405" t="inlineStr">
         <is>
@@ -38346,12 +38346,12 @@
       </c>
       <c r="T405" t="inlineStr">
         <is>
-          <t>1136467711</t>
+          <t>2008641686</t>
         </is>
       </c>
       <c r="U405" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136467711</t>
+          <t>https://m.place.naver.com/place/2008641686</t>
         </is>
       </c>
       <c r="V405" t="inlineStr">
@@ -38368,39 +38368,39 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>단비네펫살롱</t>
+          <t>깨독</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>danbine_petsalon@naver.com</t>
+          <t>koreai815@naver.com</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr">
         <is>
-          <t>0507-1399-3567</t>
+          <t>0507-1361-2731</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 충렬대로107번길 65 동래래미안아이파크상가317동203호</t>
+          <t>부산광역시 동래구 사직로 80 222동 B206호</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s4Fys2jg</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -38416,22 +38416,22 @@
       <c r="M406" t="inlineStr"/>
       <c r="N406" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P406" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q406" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="R406" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
@@ -38440,12 +38440,12 @@
       </c>
       <c r="T406" t="inlineStr">
         <is>
-          <t>1761335157</t>
+          <t>1136467711</t>
         </is>
       </c>
       <c r="U406" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1761335157</t>
+          <t>https://m.place.naver.com/place/1136467711</t>
         </is>
       </c>
       <c r="V406" t="inlineStr">
@@ -38462,34 +38462,34 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>오늘더 빛나개</t>
+          <t>단비네펫살롱</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>genefit_@naver.com</t>
+          <t>danbine_petsalon@naver.com</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr">
         <is>
-          <t>0507-1335-2650</t>
+          <t>0507-1399-3567</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
       <c r="G407" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 충렬대로410번길 31-4 1층</t>
+          <t>부산광역시 동래구 충렬대로107번길 65 동래래미안아이파크상가317동203호</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/shine_petshop</t>
+          <t>https://open.kakao.com/o/s4Fys2jg</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
@@ -38510,7 +38510,7 @@
       <c r="M407" t="inlineStr"/>
       <c r="N407" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O407" t="inlineStr">
@@ -38519,13 +38519,13 @@
         </is>
       </c>
       <c r="P407" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="Q407" t="n">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="R407" t="n">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="S407" t="inlineStr">
         <is>
@@ -38534,12 +38534,12 @@
       </c>
       <c r="T407" t="inlineStr">
         <is>
-          <t>1429492286</t>
+          <t>1761335157</t>
         </is>
       </c>
       <c r="U407" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429492286</t>
+          <t>https://m.place.naver.com/place/1761335157</t>
         </is>
       </c>
       <c r="V407" t="inlineStr">
@@ -38556,25 +38556,29 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>멍뭉</t>
+          <t>오늘더 빛나개</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>zjvl851@naver.com</t>
+          <t>genefit_@naver.com</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
-      <c r="E408" t="inlineStr"/>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>0507-1335-2650</t>
+        </is>
+      </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 아시아드대로255번길 14 상가105동 103-2호</t>
+          <t>부산광역시 동래구 충렬대로410번길 31-4 1층</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/shine_petshop</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -38584,7 +38588,7 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
@@ -38605,17 +38609,17 @@
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P408" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Q408" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R408" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="S408" t="inlineStr">
         <is>
@@ -38624,12 +38628,12 @@
       </c>
       <c r="T408" t="inlineStr">
         <is>
-          <t>2006663990</t>
+          <t>1429492286</t>
         </is>
       </c>
       <c r="U408" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2006663990</t>
+          <t>https://m.place.naver.com/place/1429492286</t>
         </is>
       </c>
       <c r="V408" t="inlineStr">
@@ -38646,29 +38650,25 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>메리몰펫샵 사직점</t>
+          <t>멍뭉</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>merrymallpetshop_no5@naver.com</t>
+          <t>zjvl851@naver.com</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>0507-1391-4011</t>
-        </is>
-      </c>
+      <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 쇠미로60번길 53 1동 1층 101호</t>
+          <t>부산광역시 동래구 아시아드대로255번길 14 상가105동 103-2호</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/merrymallpetshop_no5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -38678,12 +38678,12 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
@@ -38699,17 +38699,17 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P409" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="Q409" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="R409" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="S409" t="inlineStr">
         <is>
@@ -38718,12 +38718,12 @@
       </c>
       <c r="T409" t="inlineStr">
         <is>
-          <t>1197098664</t>
+          <t>2006663990</t>
         </is>
       </c>
       <c r="U409" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197098664</t>
+          <t>https://m.place.naver.com/place/2006663990</t>
         </is>
       </c>
       <c r="V409" t="inlineStr">
@@ -38740,29 +38740,29 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>위드미몽몽</t>
+          <t>메리몰펫샵 사직점</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>s__mn0@naver.com</t>
+          <t>merrymallpetshop_no5@naver.com</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0507-1480-3321</t>
+          <t>0507-1391-4011</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 온천천로339번길 51 202동 1층 14호</t>
+          <t>부산광역시 동래구 쇠미로60번길 53 1동 1층 101호</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/merrymallpetshop_no5</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -38772,12 +38772,12 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -38793,17 +38793,17 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P410" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="Q410" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R410" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="S410" t="inlineStr">
         <is>
@@ -38812,12 +38812,12 @@
       </c>
       <c r="T410" t="inlineStr">
         <is>
-          <t>2044973352</t>
+          <t>1197098664</t>
         </is>
       </c>
       <c r="U410" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044973352</t>
+          <t>https://m.place.naver.com/place/1197098664</t>
         </is>
       </c>
       <c r="V410" t="inlineStr">
@@ -38834,29 +38834,29 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>몽몽펫살롱</t>
+          <t>위드미몽몽</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>mongpetsalon@naver.com</t>
+          <t>s__mn0@naver.com</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0507-1494-1556</t>
+          <t>0507-1480-3321</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
       <c r="G411" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 충렬대로202번길 31 1층</t>
+          <t>부산광역시 동래구 온천천로339번길 51 202동 1층 14호</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mong_petsalon?igsh=MXR4OHZyd3RoZDRiYQ==</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -38866,7 +38866,7 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
@@ -38887,17 +38887,17 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P411" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="Q411" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R411" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="S411" t="inlineStr">
         <is>
@@ -38906,12 +38906,12 @@
       </c>
       <c r="T411" t="inlineStr">
         <is>
-          <t>2063533369</t>
+          <t>2044973352</t>
         </is>
       </c>
       <c r="U411" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2063533369</t>
+          <t>https://m.place.naver.com/place/2044973352</t>
         </is>
       </c>
       <c r="V411" t="inlineStr">
@@ -38928,39 +38928,39 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>메리몰펫샵 안락점</t>
+          <t>몽몽펫살롱</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>jjung_lee82@naver.com</t>
+          <t>mongpetsalon@naver.com</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>0507-1344-4865</t>
+          <t>0507-1494-1556</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 안락로125번가길 18 1층</t>
+          <t>부산광역시 동래구 충렬대로202번길 31 1층</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>https://link.groomernote.com/merrymallpetshop_no11</t>
+          <t>https://www.instagram.com/mong_petsalon?igsh=MXR4OHZyd3RoZDRiYQ==</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -38988,10 +38988,10 @@
         <v>35</v>
       </c>
       <c r="Q412" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="R412" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="S412" t="inlineStr">
         <is>
@@ -39000,12 +39000,12 @@
       </c>
       <c r="T412" t="inlineStr">
         <is>
-          <t>1868452852</t>
+          <t>2063533369</t>
         </is>
       </c>
       <c r="U412" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868452852</t>
+          <t>https://m.place.naver.com/place/2063533369</t>
         </is>
       </c>
       <c r="V412" t="inlineStr">
@@ -39022,39 +39022,39 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>에드펫살롱</t>
+          <t>메리몰펫샵 안락점</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>mungnyang_salon@naver.com</t>
+          <t>jjung_lee82@naver.com</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0507-1402-0076</t>
+          <t>0507-1344-4865</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 여고북로 211-2 1층</t>
+          <t>부산광역시 동래구 안락로125번가길 18 1층</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aidepetsalon</t>
+          <t>https://link.groomernote.com/merrymallpetshop_no11</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
@@ -39079,13 +39079,13 @@
         </is>
       </c>
       <c r="P413" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="Q413" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="R413" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="S413" t="inlineStr">
         <is>
@@ -39094,12 +39094,12 @@
       </c>
       <c r="T413" t="inlineStr">
         <is>
-          <t>1223970524</t>
+          <t>1868452852</t>
         </is>
       </c>
       <c r="U413" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1223970524</t>
+          <t>https://m.place.naver.com/place/1868452852</t>
         </is>
       </c>
       <c r="V413" t="inlineStr">
@@ -39111,30 +39111,34 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>반려동물분양</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>부산강아지분양 하이퍼피</t>
+          <t>에드펫살롱</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>hipuppy6474@naver.com</t>
+          <t>mungnyang_salon@naver.com</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>0507-1402-0076</t>
+        </is>
+      </c>
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 사직북로57번길 4 1층</t>
+          <t>부산광역시 동래구 여고북로 211-2 1층</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hipuppy6474/223682503066</t>
+          <t>https://www.instagram.com/aidepetsalon</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -39149,7 +39153,7 @@
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
@@ -39169,13 +39173,13 @@
         </is>
       </c>
       <c r="P414" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="Q414" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="R414" t="n">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="S414" t="inlineStr">
         <is>
@@ -39184,12 +39188,12 @@
       </c>
       <c r="T414" t="inlineStr">
         <is>
-          <t>1271036891</t>
+          <t>1223970524</t>
         </is>
       </c>
       <c r="U414" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1271036891</t>
+          <t>https://m.place.naver.com/place/1223970524</t>
         </is>
       </c>
       <c r="V414" t="inlineStr">
@@ -39201,17 +39205,17 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>반려동물분양</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>중앙이용원</t>
+          <t>부산강아지분양 하이퍼피</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>aqualjs1@naver.com</t>
+          <t>hipuppy6474@naver.com</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -39219,12 +39223,12 @@
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 시실로211번길 59-2</t>
+          <t>부산광역시 동래구 사직북로57번길 4 1층</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/hipuppy6474/223682503066</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -39234,12 +39238,12 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
@@ -39255,17 +39259,17 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P415" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="Q415" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="R415" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="S415" t="inlineStr">
         <is>
@@ -39274,12 +39278,12 @@
       </c>
       <c r="T415" t="inlineStr">
         <is>
-          <t>16806172</t>
+          <t>1271036891</t>
         </is>
       </c>
       <c r="U415" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16806172</t>
+          <t>https://m.place.naver.com/place/1271036891</t>
         </is>
       </c>
       <c r="V415" t="inlineStr">
@@ -39296,12 +39300,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>동래이발</t>
+          <t>중앙이용원</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>ljheeljhee@naver.com</t>
+          <t>aqualjs1@naver.com</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
@@ -39309,7 +39313,7 @@
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 충렬대로271번길 61</t>
+          <t>부산광역시 동래구 시실로211번길 59-2</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -39349,13 +39353,13 @@
         </is>
       </c>
       <c r="P416" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q416" t="n">
         <v>0</v>
       </c>
       <c r="R416" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S416" t="inlineStr">
         <is>
@@ -39364,12 +39368,12 @@
       </c>
       <c r="T416" t="inlineStr">
         <is>
-          <t>1969624990</t>
+          <t>16806172</t>
         </is>
       </c>
       <c r="U416" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1969624990</t>
+          <t>https://m.place.naver.com/place/16806172</t>
         </is>
       </c>
       <c r="V416" t="inlineStr">
@@ -39386,24 +39390,20 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>명장이발</t>
+          <t>동래이발</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>sdupr@naver.com</t>
+          <t>ljheeljhee@naver.com</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>051-2364-8529</t>
-        </is>
-      </c>
+      <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 시실로211번길 5</t>
+          <t>부산광역시 동래구 충렬대로271번길 61</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -39443,13 +39443,13 @@
         </is>
       </c>
       <c r="P417" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R417" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S417" t="inlineStr">
         <is>
@@ -39458,12 +39458,12 @@
       </c>
       <c r="T417" t="inlineStr">
         <is>
-          <t>1582366405</t>
+          <t>1969624990</t>
         </is>
       </c>
       <c r="U417" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1582366405</t>
+          <t>https://m.place.naver.com/place/1969624990</t>
         </is>
       </c>
       <c r="V417" t="inlineStr">
@@ -39480,29 +39480,29 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>익스너그바버샵</t>
+          <t>명장이발</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>dbstn520@naver.com</t>
+          <t>sdupr@naver.com</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr">
         <is>
-          <t>0507-1343-8757</t>
+          <t>051-2364-8529</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
       <c r="G418" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 명륜로 119-1 1층</t>
+          <t>부산광역시 동래구 시실로211번길 5</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/iksnugbarbershop</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -39512,7 +39512,7 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
@@ -39533,17 +39533,17 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P418" t="n">
-        <v>352</v>
+        <v>2</v>
       </c>
       <c r="Q418" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="R418" t="n">
-        <v>373</v>
+        <v>3</v>
       </c>
       <c r="S418" t="inlineStr">
         <is>
@@ -39552,12 +39552,12 @@
       </c>
       <c r="T418" t="inlineStr">
         <is>
-          <t>1098870223</t>
+          <t>1582366405</t>
         </is>
       </c>
       <c r="U418" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098870223</t>
+          <t>https://m.place.naver.com/place/1582366405</t>
         </is>
       </c>
       <c r="V418" t="inlineStr">
@@ -39574,25 +39574,29 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>명일이발관</t>
+          <t>익스너그바버샵</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>highestfit@naver.com</t>
+          <t>dbstn520@naver.com</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
-      <c r="E419" t="inlineStr"/>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>0507-1343-8757</t>
+        </is>
+      </c>
       <c r="F419" t="inlineStr"/>
       <c r="G419" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 명안로77번길 29</t>
+          <t>부산광역시 동래구 명륜로 119-1 1층</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/iksnugbarbershop</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -39602,7 +39606,7 @@
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
@@ -39623,17 +39627,17 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P419" t="n">
-        <v>1</v>
+        <v>352</v>
       </c>
       <c r="Q419" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R419" t="n">
-        <v>1</v>
+        <v>373</v>
       </c>
       <c r="S419" t="inlineStr">
         <is>
@@ -39642,12 +39646,12 @@
       </c>
       <c r="T419" t="inlineStr">
         <is>
-          <t>16805885</t>
+          <t>1098870223</t>
         </is>
       </c>
       <c r="U419" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16805885</t>
+          <t>https://m.place.naver.com/place/1098870223</t>
         </is>
       </c>
       <c r="V419" t="inlineStr">
@@ -39664,29 +39668,25 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>도트바버샵</t>
+          <t>명일이발관</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>jihae0301@naver.com</t>
+          <t>highestfit@naver.com</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>0507-1348-6474</t>
-        </is>
-      </c>
+      <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 금강공원로 7 2층</t>
+          <t>부산광역시 동래구 명안로77번길 29</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barber_ayaan</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -39696,7 +39696,7 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
@@ -39717,17 +39717,17 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P420" t="n">
-        <v>309</v>
+        <v>1</v>
       </c>
       <c r="Q420" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="R420" t="n">
-        <v>399</v>
+        <v>1</v>
       </c>
       <c r="S420" t="inlineStr">
         <is>
@@ -39736,12 +39736,12 @@
       </c>
       <c r="T420" t="inlineStr">
         <is>
-          <t>1181393447</t>
+          <t>16805885</t>
         </is>
       </c>
       <c r="U420" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1181393447</t>
+          <t>https://m.place.naver.com/place/16805885</t>
         </is>
       </c>
       <c r="V420" t="inlineStr">
@@ -39758,29 +39758,29 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>코리아넘버원바버샵</t>
+          <t>도트바버샵</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>kbhnews-@naver.com</t>
+          <t>jihae0301@naver.com</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr">
         <is>
-          <t>051-532-4990</t>
+          <t>0507-1348-6474</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 충렬대로410번길 60</t>
+          <t>부산광역시 동래구 금강공원로 7 2층</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/barber_ayaan</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -39790,7 +39790,7 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
@@ -39811,17 +39811,17 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P421" t="n">
-        <v>7</v>
+        <v>309</v>
       </c>
       <c r="Q421" t="n">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="R421" t="n">
-        <v>10</v>
+        <v>399</v>
       </c>
       <c r="S421" t="inlineStr">
         <is>
@@ -39830,12 +39830,12 @@
       </c>
       <c r="T421" t="inlineStr">
         <is>
-          <t>1537657502</t>
+          <t>1181393447</t>
         </is>
       </c>
       <c r="U421" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537657502</t>
+          <t>https://m.place.naver.com/place/1181393447</t>
         </is>
       </c>
       <c r="V421" t="inlineStr">
@@ -39852,24 +39852,24 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>평화이용원</t>
+          <t>코리아넘버원바버샵</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>seogwipo-si@naver.com</t>
+          <t>kbhnews-@naver.com</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr">
         <is>
-          <t>051-557-2813</t>
+          <t>051-532-4990</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
       <c r="G422" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 칠산동 331-4</t>
+          <t>부산광역시 동래구 충렬대로410번길 60</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -39909,13 +39909,13 @@
         </is>
       </c>
       <c r="P422" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q422" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R422" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S422" t="inlineStr">
         <is>
@@ -39924,12 +39924,12 @@
       </c>
       <c r="T422" t="inlineStr">
         <is>
-          <t>16492977</t>
+          <t>1537657502</t>
         </is>
       </c>
       <c r="U422" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16492977</t>
+          <t>https://m.place.naver.com/place/1537657502</t>
         </is>
       </c>
       <c r="V422" t="inlineStr">
@@ -39946,29 +39946,29 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>갓더숍바버샵</t>
+          <t>평화이용원</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>godtheshop@naver.com</t>
+          <t>seogwipo-si@naver.com</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
-          <t>0507-1362-3821</t>
+          <t>051-557-2813</t>
         </is>
       </c>
       <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 명륜로103번길 4 2층 갓더숍</t>
+          <t>부산광역시 동래구 칠산동 331-4</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/godtheshop_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -39978,7 +39978,7 @@
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
@@ -39999,17 +39999,17 @@
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P423" t="n">
-        <v>702</v>
+        <v>1</v>
       </c>
       <c r="Q423" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R423" t="n">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="S423" t="inlineStr">
         <is>
@@ -40018,12 +40018,12 @@
       </c>
       <c r="T423" t="inlineStr">
         <is>
-          <t>1802772637</t>
+          <t>16492977</t>
         </is>
       </c>
       <c r="U423" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1802772637</t>
+          <t>https://m.place.naver.com/place/16492977</t>
         </is>
       </c>
       <c r="V423" t="inlineStr">
@@ -40040,34 +40040,34 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>레드폴바버샵 부산동래점</t>
+          <t>갓더숍바버샵</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>redpole_barber@naver.com</t>
+          <t>godtheshop@naver.com</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr">
         <is>
-          <t>051-668-4409</t>
+          <t>0507-1362-3821</t>
         </is>
       </c>
       <c r="F424" t="inlineStr"/>
       <c r="G424" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 중앙대로 1393 롯데백화점 동래점 4층</t>
+          <t>부산광역시 동래구 명륜로103번길 4 2층 갓더숍</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>http://dhd9711.cafe24.com/barber/</t>
+          <t>https://www.instagram.com/godtheshop_</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
@@ -40077,7 +40077,7 @@
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
@@ -40097,13 +40097,13 @@
         </is>
       </c>
       <c r="P424" t="n">
-        <v>565</v>
+        <v>702</v>
       </c>
       <c r="Q424" t="n">
-        <v>181</v>
+        <v>4</v>
       </c>
       <c r="R424" t="n">
-        <v>746</v>
+        <v>706</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
@@ -40112,12 +40112,12 @@
       </c>
       <c r="T424" t="inlineStr">
         <is>
-          <t>1902869372</t>
+          <t>1802772637</t>
         </is>
       </c>
       <c r="U424" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1902869372</t>
+          <t>https://m.place.naver.com/place/1802772637</t>
         </is>
       </c>
       <c r="V424" t="inlineStr">
@@ -40134,40 +40134,44 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>진주이용원</t>
+          <t>레드폴바버샵 부산동래점</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>gtour_guide@naver.com</t>
+          <t>redpole_barber@naver.com</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
-      <c r="E425" t="inlineStr"/>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>051-668-4409</t>
+        </is>
+      </c>
       <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 명륜로112번길 133</t>
+          <t>부산광역시 동래구 중앙대로 1393 롯데백화점 동래점 4층</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://dhd9711.cafe24.com/barber/</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
@@ -40183,17 +40187,17 @@
       </c>
       <c r="O425" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P425" t="n">
-        <v>0</v>
+        <v>565</v>
       </c>
       <c r="Q425" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="R425" t="n">
-        <v>0</v>
+        <v>746</v>
       </c>
       <c r="S425" t="inlineStr">
         <is>
@@ -40202,12 +40206,12 @@
       </c>
       <c r="T425" t="inlineStr">
         <is>
-          <t>16812761</t>
+          <t>1902869372</t>
         </is>
       </c>
       <c r="U425" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16812761</t>
+          <t>https://m.place.naver.com/place/1902869372</t>
         </is>
       </c>
       <c r="V425" t="inlineStr">
@@ -40224,29 +40228,25 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>그랑불바버샵</t>
+          <t>진주이용원</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>6616sms@naver.com</t>
+          <t>gtour_guide@naver.com</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>0507-1315-6480</t>
-        </is>
-      </c>
+      <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 명륜로129번길 3 3층</t>
+          <t>부산광역시 동래구 명륜로112번길 133</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/grandbull_barbershop</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -40256,7 +40256,7 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
@@ -40277,17 +40277,17 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P426" t="n">
-        <v>1815</v>
+        <v>0</v>
       </c>
       <c r="Q426" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="R426" t="n">
-        <v>1934</v>
+        <v>0</v>
       </c>
       <c r="S426" t="inlineStr">
         <is>
@@ -40296,12 +40296,12 @@
       </c>
       <c r="T426" t="inlineStr">
         <is>
-          <t>1190845854</t>
+          <t>16812761</t>
         </is>
       </c>
       <c r="U426" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1190845854</t>
+          <t>https://m.place.naver.com/place/16812761</t>
         </is>
       </c>
       <c r="V426" t="inlineStr">
@@ -40318,29 +40318,29 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>문화이용원</t>
+          <t>그랑불바버샵</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>suwonloves@naver.com</t>
+          <t>6616sms@naver.com</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
-          <t>051-554-2834</t>
+          <t>0507-1315-6480</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 온천천로319번길 35</t>
+          <t>부산광역시 동래구 명륜로129번길 3 3층</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/grandbull_barbershop</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
@@ -40371,17 +40371,17 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P427" t="n">
-        <v>0</v>
+        <v>1815</v>
       </c>
       <c r="Q427" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="R427" t="n">
-        <v>0</v>
+        <v>1934</v>
       </c>
       <c r="S427" t="inlineStr">
         <is>
@@ -40390,12 +40390,12 @@
       </c>
       <c r="T427" t="inlineStr">
         <is>
-          <t>1898764943</t>
+          <t>1190845854</t>
         </is>
       </c>
       <c r="U427" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1898764943</t>
+          <t>https://m.place.naver.com/place/1190845854</t>
         </is>
       </c>
       <c r="V427" t="inlineStr">
@@ -40412,29 +40412,29 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>리차드맨즈헤어 바버샵</t>
+          <t>문화이용원</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>ninano40@naver.com</t>
+          <t>suwonloves@naver.com</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>0507-1375-6647</t>
+          <t>051-554-2834</t>
         </is>
       </c>
       <c r="F428" t="inlineStr"/>
       <c r="G428" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 차밭골로 19 2층</t>
+          <t>부산광역시 동래구 온천천로319번길 35</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jeonsiu8166_hair</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -40444,7 +40444,7 @@
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
@@ -40465,17 +40465,17 @@
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P428" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="Q428" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R428" t="n">
-        <v>468</v>
+        <v>0</v>
       </c>
       <c r="S428" t="inlineStr">
         <is>
@@ -40484,12 +40484,12 @@
       </c>
       <c r="T428" t="inlineStr">
         <is>
-          <t>1722779284</t>
+          <t>1898764943</t>
         </is>
       </c>
       <c r="U428" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722779284</t>
+          <t>https://m.place.naver.com/place/1898764943</t>
         </is>
       </c>
       <c r="V428" t="inlineStr">
@@ -40506,25 +40506,29 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>멋진남자헤어</t>
+          <t>리차드맨즈헤어 바버샵</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>doublesholdings@naver.com</t>
+          <t>ninano40@naver.com</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
-      <c r="E429" t="inlineStr"/>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>0507-1375-6647</t>
+        </is>
+      </c>
       <c r="F429" t="inlineStr"/>
       <c r="G429" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 명안로53번길 71 1층 멋진남자헤어</t>
+          <t>부산광역시 동래구 차밭골로 19 2층</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jeonsiu8166_hair</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -40534,7 +40538,7 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
@@ -40555,17 +40559,17 @@
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P429" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="Q429" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="R429" t="n">
-        <v>1</v>
+        <v>468</v>
       </c>
       <c r="S429" t="inlineStr">
         <is>
@@ -40574,12 +40578,12 @@
       </c>
       <c r="T429" t="inlineStr">
         <is>
-          <t>1934399805</t>
+          <t>1722779284</t>
         </is>
       </c>
       <c r="U429" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1934399805</t>
+          <t>https://m.place.naver.com/place/1722779284</t>
         </is>
       </c>
       <c r="V429" t="inlineStr">
@@ -40596,29 +40600,25 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>금강이발</t>
+          <t>멋진남자헤어</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>kumkangbarbers@naver.com</t>
+          <t>doublesholdings@naver.com</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>070-4833-4878</t>
-        </is>
-      </c>
+      <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 금강로74번길 13 1층 금강이발</t>
+          <t>부산광역시 동래구 명안로53번길 71 1층 멋진남자헤어</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kumkangbarbers</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -40628,12 +40628,12 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
@@ -40649,17 +40649,17 @@
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P430" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="Q430" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R430" t="n">
-        <v>188</v>
+        <v>1</v>
       </c>
       <c r="S430" t="inlineStr">
         <is>
@@ -40668,12 +40668,12 @@
       </c>
       <c r="T430" t="inlineStr">
         <is>
-          <t>2007321729</t>
+          <t>1934399805</t>
         </is>
       </c>
       <c r="U430" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007321729</t>
+          <t>https://m.place.naver.com/place/1934399805</t>
         </is>
       </c>
       <c r="V430" t="inlineStr">
@@ -40690,29 +40690,29 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>치웨크맨즈헤어 바버샵</t>
+          <t>금강이발</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>czlek0516@naver.com</t>
+          <t>kumkangbarbers@naver.com</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0507-1492-0516</t>
+          <t>070-4833-4878</t>
         </is>
       </c>
       <c r="F431" t="inlineStr"/>
       <c r="G431" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 온천장로 100 A동 3층</t>
+          <t>부산광역시 동래구 금강로74번길 13 1층 금강이발</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>http://instagram.com/czlek_mens_hair/</t>
+          <t>https://blog.naver.com/kumkangbarbers</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -40727,7 +40727,7 @@
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
@@ -40747,13 +40747,13 @@
         </is>
       </c>
       <c r="P431" t="n">
-        <v>659</v>
+        <v>158</v>
       </c>
       <c r="Q431" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="R431" t="n">
-        <v>789</v>
+        <v>188</v>
       </c>
       <c r="S431" t="inlineStr">
         <is>
@@ -40762,12 +40762,12 @@
       </c>
       <c r="T431" t="inlineStr">
         <is>
-          <t>1024919608</t>
+          <t>2007321729</t>
         </is>
       </c>
       <c r="U431" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024919608</t>
+          <t>https://m.place.naver.com/place/2007321729</t>
         </is>
       </c>
       <c r="V431" t="inlineStr">
@@ -40779,49 +40779,49 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>공간다올 부산</t>
+          <t>치웨크맨즈헤어 바버샵</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>daol_24@naver.com</t>
+          <t>czlek0516@naver.com</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>0507-1413-0789</t>
+          <t>0507-1492-0516</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
       <c r="G432" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 반송로171번길 3</t>
+          <t>부산광역시 동래구 온천장로 100 A동 3층</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>https://daol24.itpage.kr/</t>
+          <t>http://instagram.com/czlek_mens_hair/</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
@@ -40841,13 +40841,13 @@
         </is>
       </c>
       <c r="P432" t="n">
-        <v>1</v>
+        <v>659</v>
       </c>
       <c r="Q432" t="n">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="R432" t="n">
-        <v>22</v>
+        <v>789</v>
       </c>
       <c r="S432" t="inlineStr">
         <is>
@@ -40856,12 +40856,12 @@
       </c>
       <c r="T432" t="inlineStr">
         <is>
-          <t>13426230</t>
+          <t>1024919608</t>
         </is>
       </c>
       <c r="U432" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13426230</t>
+          <t>https://m.place.naver.com/place/1024919608</t>
         </is>
       </c>
       <c r="V432" t="inlineStr">
@@ -40878,29 +40878,29 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>두민디자인</t>
+          <t>공간다올 부산</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>kimsint210@naver.com</t>
+          <t>daol_24@naver.com</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>051-851-7873</t>
+          <t>0507-1413-0789</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 충렬대로 268 2층 두민디자인</t>
+          <t>부산광역시 동래구 반송로171번길 3</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>http://www.dumindesign.co.kr/</t>
+          <t>https://daol24.itpage.kr/</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -40910,7 +40910,7 @@
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
@@ -40931,34 +40931,128 @@
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P433" t="n">
         <v>1</v>
       </c>
       <c r="Q433" t="n">
+        <v>21</v>
+      </c>
+      <c r="R433" t="n">
+        <v>22</v>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>13426230</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13426230</t>
+        </is>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>두민디자인</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>kimsint210@naver.com</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>051-851-7873</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>부산광역시 동래구 충렬대로 268 2층 두민디자인</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>http://www.dumindesign.co.kr/</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr"/>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P434" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q434" t="n">
         <v>2</v>
       </c>
-      <c r="R433" t="n">
+      <c r="R434" t="n">
         <v>3</v>
       </c>
-      <c r="S433" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T433" t="inlineStr">
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
         <is>
           <t>13452577</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="U434" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/13452577</t>
         </is>
       </c>
-      <c r="V433" t="inlineStr">
+      <c r="V434" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
